--- a/data/test/structured/time_mapping.xlsx
+++ b/data/test/structured/time_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>原始起点</t>
+          <t>样本起点</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>原始终点</t>
+          <t>样本终点</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -456,37 +456,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>合成微信流水</t>
+          <t>测试结构化银行流水和通话记录</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-08-10 00:00:00</t>
+          <t>2023-08-31 00:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-09-10 23:59:59</t>
+          <t>2024-09-20 23:59:59</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-08-10 00:00:00</t>
+          <t>2007-08-31 00:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2024-09-10 23:59:59</t>
+          <t>2008-09-20 23:59:59</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>案情整体后移，微信交易时间即案情时间。</t>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HISTORY-16Y</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>案情梳理历史背景</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1999-07-09</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2008-10-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>保留原案多年监管失职和案发后徇私处置的时间比例。</t>
         </is>
       </c>
     </row>

--- a/data/test/structured/time_mapping.xlsx
+++ b/data/test/structured/time_mapping.xlsx
@@ -413,117 +413,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>规则ID</t>
+          <t>??ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>适用条件</t>
+          <t>????</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>样本起点</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>样本终点</t>
+          <t>????</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>案情起点</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>案情终点</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>??</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>测试结构化银行流水和通话记录</t>
+          <t>??????????????</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2007-08-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2008-10-25 23:59:59</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>2023-08-31 00:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024-09-20 23:59:59</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2007-08-31 00:00:00</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2008-09-20 23:59:59</t>
+          <t>2024-10-25 23:59:59</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HISTORY-16Y</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>案情梳理历史背景</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1999-07-09</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2008-10-25</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>保留原案多年监管失职和案发后徇私处置的时间比例。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
     </row>
